--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D353"/>
+  <dimension ref="A1:D355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5612,7 +5612,7 @@
         <v>1691.28</v>
       </c>
       <c r="C324" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D324" t="n">
         <v>12</v>
@@ -5644,7 +5644,7 @@
         <v>1775.77</v>
       </c>
       <c r="C326" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D326" t="n">
         <v>7</v>
@@ -5660,7 +5660,7 @@
         <v>1922.66</v>
       </c>
       <c r="C327" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D327" t="n">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1841.7</v>
+        <v>1843.32</v>
       </c>
       <c r="C352" t="n">
         <v>298</v>
@@ -6073,13 +6073,45 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1842.25</v>
+        <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1924.82</v>
+      </c>
+      <c r="C354" t="n">
+        <v>297</v>
+      </c>
+      <c r="D354" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>2096.29</v>
+      </c>
+      <c r="C355" t="n">
+        <v>326</v>
+      </c>
+      <c r="D355" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5612,7 +5612,7 @@
         <v>1691.28</v>
       </c>
       <c r="C324" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D324" t="n">
         <v>12</v>
@@ -5644,7 +5644,7 @@
         <v>1775.77</v>
       </c>
       <c r="C326" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D326" t="n">
         <v>7</v>
@@ -5660,7 +5660,7 @@
         <v>1922.66</v>
       </c>
       <c r="C327" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D327" t="n">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1924.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2096.29</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5644,7 +5644,7 @@
         <v>1775.77</v>
       </c>
       <c r="C326" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D326" t="n">
         <v>7</v>
@@ -5660,7 +5660,7 @@
         <v>1922.66</v>
       </c>
       <c r="C327" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D327" t="n">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>1924.82</v>
+        <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6105,12 +6105,28 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2096.29</v>
+        <v>2140.51</v>
       </c>
       <c r="C355" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>1715.5</v>
+      </c>
+      <c r="C356" t="n">
+        <v>294</v>
+      </c>
+      <c r="D356" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5644,7 +5644,7 @@
         <v>1775.77</v>
       </c>
       <c r="C326" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D326" t="n">
         <v>7</v>
@@ -5660,7 +5660,7 @@
         <v>1922.66</v>
       </c>
       <c r="C327" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D327" t="n">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2140.51</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5644,7 +5644,7 @@
         <v>1775.77</v>
       </c>
       <c r="C326" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D326" t="n">
         <v>7</v>
@@ -5660,7 +5660,7 @@
         <v>1922.66</v>
       </c>
       <c r="C327" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D327" t="n">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2140.51</v>
+        <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6121,13 +6121,29 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>1715.5</v>
+        <v>1765.37</v>
       </c>
       <c r="C356" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D356" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1733.24</v>
+      </c>
+      <c r="C357" t="n">
+        <v>308</v>
+      </c>
+      <c r="D357" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D357"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>1765.37</v>
+        <v>1767.24</v>
       </c>
       <c r="C356" t="n">
         <v>297</v>
@@ -6137,13 +6137,29 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1733.24</v>
+        <v>1766.09</v>
       </c>
       <c r="C357" t="n">
         <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1744.96</v>
+      </c>
+      <c r="C358" t="n">
+        <v>303</v>
+      </c>
+      <c r="D358" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5644,7 +5644,7 @@
         <v>1775.77</v>
       </c>
       <c r="C326" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D326" t="n">
         <v>7</v>
@@ -5660,7 +5660,7 @@
         <v>1922.66</v>
       </c>
       <c r="C327" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D327" t="n">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1744.96</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D358"/>
+  <dimension ref="A1:D359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6153,13 +6153,29 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1744.96</v>
+        <v>1768.07</v>
       </c>
       <c r="C358" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1868.52</v>
+      </c>
+      <c r="C359" t="n">
+        <v>305</v>
+      </c>
+      <c r="D359" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5676,7 +5676,7 @@
         <v>1684.53</v>
       </c>
       <c r="C328" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5692,7 +5692,7 @@
         <v>1702.59</v>
       </c>
       <c r="C329" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D329" t="n">
         <v>6</v>
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1768.07</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1868.52</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D359"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1768.07</v>
+        <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6169,13 +6169,45 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>1868.52</v>
+        <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>2051.12</v>
+      </c>
+      <c r="C360" t="n">
+        <v>326</v>
+      </c>
+      <c r="D360" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>2200.72</v>
+      </c>
+      <c r="C361" t="n">
+        <v>328</v>
+      </c>
+      <c r="D361" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2200.72</v>
       </c>
       <c r="C361" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>2051.12</v>
+        <v>2056.18</v>
       </c>
       <c r="C360" t="n">
         <v>326</v>
@@ -6201,13 +6201,29 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>2200.72</v>
+        <v>2240.83</v>
       </c>
       <c r="C361" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1861.49</v>
+      </c>
+      <c r="C362" t="n">
+        <v>321</v>
+      </c>
+      <c r="D362" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>2240.83</v>
+        <v>2242.11</v>
       </c>
       <c r="C361" t="n">
         <v>331</v>
@@ -6217,12 +6217,28 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1861.49</v>
+        <v>1922.28</v>
       </c>
       <c r="C362" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1865.88</v>
+      </c>
+      <c r="C363" t="n">
+        <v>317</v>
+      </c>
+      <c r="D363" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5740,7 +5740,7 @@
         <v>1809.69</v>
       </c>
       <c r="C332" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D332" t="n">
         <v>9</v>
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1922.28</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1865.88</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D363"/>
+  <dimension ref="A1:D364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1922.28</v>
+        <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6233,12 +6233,28 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>1865.88</v>
+        <v>1893.53</v>
       </c>
       <c r="C363" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>1753.01</v>
+      </c>
+      <c r="C364" t="n">
+        <v>301</v>
+      </c>
+      <c r="D364" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D364"/>
+  <dimension ref="A1:D365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>1893.53</v>
+        <v>1895.55</v>
       </c>
       <c r="C363" t="n">
         <v>319</v>
@@ -6249,13 +6249,29 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>1753.01</v>
+        <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1893.05</v>
+      </c>
+      <c r="C365" t="n">
+        <v>316</v>
+      </c>
+      <c r="D365" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5772,7 +5772,7 @@
         <v>2085.18</v>
       </c>
       <c r="C334" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D365"/>
+  <dimension ref="A1:D366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6265,13 +6265,29 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>1893.05</v>
+        <v>1926.3</v>
       </c>
       <c r="C365" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D365" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>1814</v>
+      </c>
+      <c r="C366" t="n">
+        <v>296</v>
+      </c>
+      <c r="D366" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5788,7 +5788,7 @@
         <v>1916.74</v>
       </c>
       <c r="C335" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
         <v>1849.8</v>
       </c>
       <c r="C336" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1814</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D366"/>
+  <dimension ref="A1:D368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>1926.3</v>
+        <v>1927.08</v>
       </c>
       <c r="C365" t="n">
         <v>318</v>
@@ -6281,12 +6281,44 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>1814</v>
+        <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1650.44</v>
+      </c>
+      <c r="C367" t="n">
+        <v>248</v>
+      </c>
+      <c r="D367" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>1742.73</v>
+      </c>
+      <c r="C368" t="n">
+        <v>287</v>
+      </c>
+      <c r="D368" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D368"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>1650.44</v>
+        <v>1651.26</v>
       </c>
       <c r="C367" t="n">
         <v>248</v>
@@ -6313,13 +6313,29 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1742.73</v>
+        <v>1784.46</v>
       </c>
       <c r="C368" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1788.42</v>
+      </c>
+      <c r="C369" t="n">
+        <v>288</v>
+      </c>
+      <c r="D369" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5836,7 +5836,7 @@
         <v>1900.47</v>
       </c>
       <c r="C338" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1784.46</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D369"/>
+  <dimension ref="A1:D370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1784.46</v>
+        <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6329,13 +6329,29 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1788.42</v>
+        <v>1829.24</v>
       </c>
       <c r="C369" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D369" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>1719.5</v>
+      </c>
+      <c r="C370" t="n">
+        <v>297</v>
+      </c>
+      <c r="D370" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D370"/>
+  <dimension ref="A1:D371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1829.24</v>
+        <v>1828.14</v>
       </c>
       <c r="C369" t="n">
         <v>289</v>
@@ -6345,13 +6345,29 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>1719.5</v>
+        <v>1750.87</v>
       </c>
       <c r="C370" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D370" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>1578.69</v>
+      </c>
+      <c r="C371" t="n">
+        <v>303</v>
+      </c>
+      <c r="D371" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D371"/>
+  <dimension ref="A1:D372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6361,13 +6361,29 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>1578.69</v>
+        <v>1605.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1672.75</v>
+      </c>
+      <c r="C372" t="n">
+        <v>285</v>
+      </c>
+      <c r="D372" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5868,7 +5868,7 @@
         <v>1790.67</v>
       </c>
       <c r="C340" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D340" t="n">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>1892.44</v>
       </c>
       <c r="C341" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D341" t="n">
         <v>6</v>
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1605.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1672.75</v>
       </c>
       <c r="C372" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D372"/>
+  <dimension ref="A1:D373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>1605.05</v>
+        <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6377,13 +6377,29 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>1672.75</v>
+        <v>1746.41</v>
       </c>
       <c r="C372" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>1642.06</v>
+      </c>
+      <c r="C373" t="n">
+        <v>260</v>
+      </c>
+      <c r="D373" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D373"/>
+  <dimension ref="A1:D374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>1746.41</v>
+        <v>1746.99</v>
       </c>
       <c r="C372" t="n">
         <v>287</v>
@@ -6393,13 +6393,29 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1642.06</v>
+        <v>1664.07</v>
       </c>
       <c r="C373" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>1550.07</v>
+      </c>
+      <c r="C374" t="n">
+        <v>273</v>
+      </c>
+      <c r="D374" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5916,7 +5916,7 @@
         <v>1572.46</v>
       </c>
       <c r="C343" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D343" t="n">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1528.37</v>
       </c>
       <c r="C344" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D344" t="n">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>1535.92</v>
       </c>
       <c r="C345" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D345" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>1727.14</v>
       </c>
       <c r="C346" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
         <v>6</v>
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1664.07</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1550.07</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D374"/>
+  <dimension ref="A1:D377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1664.07</v>
+        <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6409,13 +6409,61 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>1550.07</v>
+        <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1700.78</v>
+      </c>
+      <c r="C375" t="n">
+        <v>260</v>
+      </c>
+      <c r="D375" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1702.31</v>
+      </c>
+      <c r="C376" t="n">
+        <v>266</v>
+      </c>
+      <c r="D376" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>1519.24</v>
+      </c>
+      <c r="C377" t="n">
+        <v>258</v>
+      </c>
+      <c r="D377" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -5980,7 +5980,7 @@
         <v>1952.28</v>
       </c>
       <c r="C347" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D347" t="n">
         <v>9</v>
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1702.31</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1519.24</v>
       </c>
       <c r="C377" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D377"/>
+  <dimension ref="A1:D378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>1702.31</v>
+        <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6457,13 +6457,29 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1519.24</v>
+        <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>1482.46</v>
+      </c>
+      <c r="C378" t="n">
+        <v>257</v>
+      </c>
+      <c r="D378" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1482.46</v>
       </c>
       <c r="C378" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D378"/>
+  <dimension ref="A1:D379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6473,12 +6473,28 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1482.46</v>
+        <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>1463.59</v>
+      </c>
+      <c r="C379" t="n">
+        <v>248</v>
+      </c>
+      <c r="D379" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6012,7 +6012,7 @@
         <v>1693.39</v>
       </c>
       <c r="C349" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D349" t="n">
         <v>4</v>
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1463.59</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D379"/>
+  <dimension ref="A1:D380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6489,13 +6489,29 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1463.59</v>
+        <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>1277.51</v>
+      </c>
+      <c r="C380" t="n">
+        <v>254</v>
+      </c>
+      <c r="D380" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6028,7 +6028,7 @@
         <v>1805.4</v>
       </c>
       <c r="C350" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D350" t="n">
         <v>8</v>
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D380"/>
+  <dimension ref="A1:D381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6505,13 +6505,29 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1277.51</v>
+        <v>1300.83</v>
       </c>
       <c r="C380" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D380" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>1280.32</v>
+      </c>
+      <c r="C381" t="n">
+        <v>262</v>
+      </c>
+      <c r="D381" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6044,7 +6044,7 @@
         <v>1765.61</v>
       </c>
       <c r="C351" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D351" t="n">
         <v>5</v>
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D381"/>
+  <dimension ref="A1:D383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1300.83</v>
+        <v>1302</v>
       </c>
       <c r="C380" t="n">
         <v>255</v>
@@ -6521,13 +6521,45 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1280.32</v>
+        <v>1324.15</v>
       </c>
       <c r="C381" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D381" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1325.5</v>
+      </c>
+      <c r="C382" t="n">
+        <v>250</v>
+      </c>
+      <c r="D382" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>1577.28</v>
+      </c>
+      <c r="C383" t="n">
+        <v>266</v>
+      </c>
+      <c r="D383" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6076,7 +6076,7 @@
         <v>1885.14</v>
       </c>
       <c r="C353" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D353" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1577.28</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D383"/>
+  <dimension ref="A1:D384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6553,13 +6553,29 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>1577.28</v>
+        <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>1209.83</v>
+      </c>
+      <c r="C384" t="n">
+        <v>251</v>
+      </c>
+      <c r="D384" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6092,7 +6092,7 @@
         <v>1925.82</v>
       </c>
       <c r="C354" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D354" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6569,13 +6569,29 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>1209.83</v>
+        <v>1230.03</v>
       </c>
       <c r="C384" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D384" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>1261.85</v>
+      </c>
+      <c r="C385" t="n">
+        <v>249</v>
+      </c>
+      <c r="D385" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6108,7 +6108,7 @@
         <v>2142.44</v>
       </c>
       <c r="C355" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D355" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1261.85</v>
       </c>
       <c r="C385" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D385"/>
+  <dimension ref="A1:D386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6569,7 +6569,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>1230.03</v>
+        <v>1230.45</v>
       </c>
       <c r="C384" t="n">
         <v>252</v>
@@ -6585,13 +6585,29 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>1261.85</v>
+        <v>1282.96</v>
       </c>
       <c r="C385" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>1314.18</v>
+      </c>
+      <c r="C386" t="n">
+        <v>256</v>
+      </c>
+      <c r="D386" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1282.96</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1314.18</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D386"/>
+  <dimension ref="A1:D387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>1282.96</v>
+        <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6601,13 +6601,29 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1314.18</v>
+        <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>1266.38</v>
+      </c>
+      <c r="C387" t="n">
+        <v>255</v>
+      </c>
+      <c r="D387" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6140,7 +6140,7 @@
         <v>1766.09</v>
       </c>
       <c r="C357" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D357" t="n">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1266.38</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D387"/>
+  <dimension ref="A1:D388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6617,13 +6617,29 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>1266.38</v>
+        <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>1470.48</v>
+      </c>
+      <c r="C388" t="n">
+        <v>253</v>
+      </c>
+      <c r="D388" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6156,7 +6156,7 @@
         <v>1769.04</v>
       </c>
       <c r="C358" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D358" t="n">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>1906</v>
       </c>
       <c r="C359" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>7</v>
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1470.48</v>
       </c>
       <c r="C388" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6633,13 +6633,45 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>1470.48</v>
+        <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>1752.23</v>
+      </c>
+      <c r="C389" t="n">
+        <v>272</v>
+      </c>
+      <c r="D389" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>1588.09</v>
+      </c>
+      <c r="C390" t="n">
+        <v>267</v>
+      </c>
+      <c r="D390" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6204,7 +6204,7 @@
         <v>2242.11</v>
       </c>
       <c r="C361" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D361" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1612.82</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1304.11</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D391"/>
+  <dimension ref="A1:D392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>1612.82</v>
+        <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6681,13 +6681,29 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>1304.11</v>
+        <v>1330.21</v>
       </c>
       <c r="C391" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>1250.34</v>
+      </c>
+      <c r="C392" t="n">
+        <v>243</v>
+      </c>
+      <c r="D392" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6220,7 +6220,7 @@
         <v>1923.93</v>
       </c>
       <c r="C362" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D362" t="n">
         <v>6</v>
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1330.21</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1250.34</v>
       </c>
       <c r="C392" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D392"/>
+  <dimension ref="A1:D393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>1330.21</v>
+        <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6697,12 +6697,28 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1250.34</v>
+        <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>1306.83</v>
+      </c>
+      <c r="C393" t="n">
+        <v>258</v>
+      </c>
+      <c r="D393" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6236,7 +6236,7 @@
         <v>1895.55</v>
       </c>
       <c r="C363" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D393"/>
+  <dimension ref="A1:D394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6713,13 +6713,29 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>1306.83</v>
+        <v>1321.57</v>
       </c>
       <c r="C393" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D393" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>1270.62</v>
+      </c>
+      <c r="C394" t="n">
+        <v>245</v>
+      </c>
+      <c r="D394" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6252,7 +6252,7 @@
         <v>1782.88</v>
       </c>
       <c r="C364" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D364" t="n">
         <v>6</v>
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6732,7 +6732,7 @@
         <v>1270.62</v>
       </c>
       <c r="C394" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D394" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D394"/>
+  <dimension ref="A1:D395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6284,7 +6284,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6729,12 +6729,28 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>1270.62</v>
+        <v>1321.33</v>
       </c>
       <c r="C394" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D394" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>1254.66</v>
+      </c>
+      <c r="C395" t="n">
+        <v>247</v>
+      </c>
+      <c r="D395" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -427,6 +427,9 @@
   </sheetPr>
   <dimension ref="A1:D395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -6284,7 +6287,7 @@
         <v>1857.91</v>
       </c>
       <c r="C366" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D366" t="n">
         <v>6</v>
@@ -6300,7 +6303,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6319,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6367,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6383,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6399,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6415,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6431,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6447,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6463,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6479,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6495,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6543,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6559,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6591,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6607,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6623,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6639,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6671,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6687,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6703,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6751,7 @@
         <v>1254.66</v>
       </c>
       <c r="C395" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,11 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D395"/>
+  <dimension ref="A1:D397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -6303,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6319,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6367,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6383,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6399,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6415,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6431,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6447,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6463,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6479,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6495,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6543,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6559,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6591,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6607,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6623,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6639,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6671,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6687,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6703,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,13 +6745,45 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>1254.66</v>
+        <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>1489.11</v>
+      </c>
+      <c r="C396" t="n">
+        <v>255</v>
+      </c>
+      <c r="D396" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>1480.84</v>
+      </c>
+      <c r="C397" t="n">
+        <v>261</v>
+      </c>
+      <c r="D397" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6300,7 +6300,7 @@
         <v>1651.26</v>
       </c>
       <c r="C367" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D367" t="n">
         <v>5</v>
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D397"/>
+  <dimension ref="A1:D398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>1489.11</v>
+        <v>1490.08</v>
       </c>
       <c r="C396" t="n">
         <v>255</v>
@@ -6777,12 +6777,28 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>1480.84</v>
+        <v>1505.92</v>
       </c>
       <c r="C397" t="n">
         <v>261</v>
       </c>
       <c r="D397" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>1169.28</v>
+      </c>
+      <c r="C398" t="n">
+        <v>234</v>
+      </c>
+      <c r="D398" t="n">
         <v>5</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6316,7 +6316,7 @@
         <v>1786.63</v>
       </c>
       <c r="C368" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D368" t="n">
         <v>6</v>
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D398"/>
+  <dimension ref="A1:D399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>
@@ -6800,6 +6800,22 @@
       </c>
       <c r="D398" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>1301.39</v>
+      </c>
+      <c r="C399" t="n">
+        <v>255</v>
+      </c>
+      <c r="D399" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>1169.28</v>
+        <v>1219.21</v>
       </c>
       <c r="C398" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D398" t="n">
         <v>5</v>
@@ -6809,13 +6809,29 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>1301.39</v>
+        <v>1313.22</v>
       </c>
       <c r="C399" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D399" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>1257.44</v>
+      </c>
+      <c r="C400" t="n">
+        <v>253</v>
+      </c>
+      <c r="D400" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>
@@ -6812,7 +6812,7 @@
         <v>1313.22</v>
       </c>
       <c r="C399" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D399" t="n">
         <v>4</v>
@@ -6828,7 +6828,7 @@
         <v>1257.44</v>
       </c>
       <c r="C400" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D400" t="n">
         <v>7</v>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D400"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>
@@ -6812,7 +6812,7 @@
         <v>1313.22</v>
       </c>
       <c r="C399" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D399" t="n">
         <v>4</v>
@@ -6825,13 +6825,29 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>1257.44</v>
+        <v>1281.68</v>
       </c>
       <c r="C400" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D400" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>1240.43</v>
+      </c>
+      <c r="C401" t="n">
+        <v>235</v>
+      </c>
+      <c r="D401" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6841,12 +6841,28 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>1240.43</v>
+        <v>1266.46</v>
       </c>
       <c r="C401" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D401" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1285.45</v>
+      </c>
+      <c r="C402" t="n">
+        <v>237</v>
+      </c>
+      <c r="D402" t="n">
         <v>5</v>
       </c>
     </row>

--- a/data-dashboard/public/data/饿了么数据.xlsx
+++ b/data-dashboard/public/data/饿了么数据.xlsx
@@ -6364,7 +6364,7 @@
         <v>1606.05</v>
       </c>
       <c r="C371" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D371" t="n">
         <v>9</v>
@@ -6380,7 +6380,7 @@
         <v>1746.99</v>
       </c>
       <c r="C372" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D372" t="n">
         <v>3</v>
@@ -6396,7 +6396,7 @@
         <v>1668.68</v>
       </c>
       <c r="C373" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D373" t="n">
         <v>2</v>
@@ -6412,7 +6412,7 @@
         <v>1574.48</v>
       </c>
       <c r="C374" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D374" t="n">
         <v>3</v>
@@ -6428,7 +6428,7 @@
         <v>1700.78</v>
       </c>
       <c r="C375" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D375" t="n">
         <v>8</v>
@@ -6444,7 +6444,7 @@
         <v>1703.84</v>
       </c>
       <c r="C376" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D376" t="n">
         <v>3</v>
@@ -6460,7 +6460,7 @@
         <v>1561.45</v>
       </c>
       <c r="C377" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D377" t="n">
         <v>4</v>
@@ -6476,7 +6476,7 @@
         <v>1501.49</v>
       </c>
       <c r="C378" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -6492,7 +6492,7 @@
         <v>1485.34</v>
       </c>
       <c r="C379" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D379" t="n">
         <v>2</v>
@@ -6540,7 +6540,7 @@
         <v>1325.5</v>
       </c>
       <c r="C382" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D382" t="n">
         <v>7</v>
@@ -6556,7 +6556,7 @@
         <v>1621.24</v>
       </c>
       <c r="C383" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D383" t="n">
         <v>5</v>
@@ -6588,7 +6588,7 @@
         <v>1285.44</v>
       </c>
       <c r="C385" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D385" t="n">
         <v>4</v>
@@ -6604,7 +6604,7 @@
         <v>1347.73</v>
       </c>
       <c r="C386" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D386" t="n">
         <v>9</v>
@@ -6620,7 +6620,7 @@
         <v>1287.51</v>
       </c>
       <c r="C387" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D387" t="n">
         <v>6</v>
@@ -6636,7 +6636,7 @@
         <v>1500.93</v>
       </c>
       <c r="C388" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D388" t="n">
         <v>8</v>
@@ -6668,7 +6668,7 @@
         <v>1614.76</v>
       </c>
       <c r="C390" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D390" t="n">
         <v>4</v>
@@ -6684,7 +6684,7 @@
         <v>1329.84</v>
       </c>
       <c r="C391" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D391" t="n">
         <v>3</v>
@@ -6700,7 +6700,7 @@
         <v>1295.17</v>
       </c>
       <c r="C392" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D392" t="n">
         <v>7</v>
@@ -6748,7 +6748,7 @@
         <v>1286.5</v>
       </c>
       <c r="C395" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D395" t="n">
         <v>6</v>
@@ -6812,7 +6812,7 @@
         <v>1313.22</v>
       </c>
       <c r="C399" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D399" t="n">
         <v>4</v>
@@ -6828,7 +6828,7 @@
         <v>1281.68</v>
       </c>
       <c r="C400" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D400" t="n">
         <v>7</v>
